--- a/input/mapping/078. OCB_GOLD_TCKH_CB_OU_DIM_HOP.xlsx
+++ b/input/mapping/078. OCB_GOLD_TCKH_CB_OU_DIM_HOP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1669" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E9F0072-B80E-4794-9E93-C65D3B21D935}"/>
+  <xr:revisionPtr revIDLastSave="1676" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59B4572A-E1B7-4CDA-A0EB-87B955F5CD77}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -227,28 +227,9 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,
-    OU_ID           STRING,
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -256,15 +237,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực (CACHE: dùng lại 2 lần trong source_data)
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
         LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite branch_information: bản mới nhất &lt;= :etl_date
-    -- (CACHE: dùng lại 2 lần trong source_data cho branch và parent branch)
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -273,7 +251,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping: bản mới nhất &lt;= :etl_date
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -284,13 +261,11 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- ou_area_mapping filter trước join (WARN 3.3)
     area_map AS (
         SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
         FROM ou_area_mapping
         WHERE CB_AREA_ID IS NOT NULL
     ),
-    -- Source data tổng hợp (CACHE: dùng lại 3 lần trong changed, new_records, close_records)
     source_data AS (
         SELECT
             h.branch_hashkey                                AS OU_ID,
@@ -318,8 +293,6 @@
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
     ),
-    -- Tập OU_ID có thay đổi thuộc tính so với bản đang active
-    -- (CACHE: dùng lại 2 lần trong new_records và close_records)
     changed AS (
         SELECT src.OU_ID
         FROM source_data src
@@ -333,8 +306,6 @@
            OR COALESCE(src.OU_ADR,      '') &lt;&gt; COALESCE(tgt.OU_ADR,      '')
            OR COALESCE(src.OU_PH,       '') &lt;&gt; COALESCE(tgt.OU_PH,       '')
     ),
-    -- Bản ghi NEW: insert mới hoặc insert version mới khi thay đổi
-    -- uuid() thay MAX+ROW_NUMBER() (fix 2.5/2.6): idempotent, không trùng khi parallel
     new_records AS (
         SELECT
             'NEW'                                               AS rec_type,
@@ -358,7 +329,6 @@
         WHERE tgt_chk.OU_ID IS NULL
            OR src.OU_ID IN (SELECT OU_ID FROM changed)
     ),
-    -- Bản ghi CLOSE: đóng version hiện tại khi có thay đổi hoặc bị xóa
     close_records AS (
         SELECT
             'CLOSE'                AS rec_type,
@@ -374,7 +344,7 @@
             tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID  -- giữ nguyên ID cũ khi close
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -383,7 +353,6 @@
                 OR src.OU_ID IS NULL
               )
     )
-    -- Liệt kê tường minh (fix 3.1: bỏ SELECT *)
     SELECT
         rec_type, CDC_FLAG,
         OU_ID, OU_NM, OU_CODE,
@@ -436,8 +405,7 @@
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>JOIN SCHEMA</t>
@@ -3496,192 +3464,192 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -3748,9 +3716,7 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
@@ -3772,7 +3738,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4137,14 +4103,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="178" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
       <c r="G1" s="151"/>
       <c r="H1" s="152"/>
       <c r="I1" s="153"/>
@@ -4189,82 +4155,82 @@
       <c r="AV1" s="39"/>
     </row>
     <row r="2" spans="1:48" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="186"/>
-      <c r="C2" s="186"/>
-      <c r="D2" s="182" t="s">
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="191" t="s">
+      <c r="E2" s="189" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="192"/>
-      <c r="G2" s="192"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
       <c r="H2" s="145"/>
     </row>
     <row r="3" spans="1:48">
-      <c r="A3" s="187"/>
-      <c r="B3" s="188"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="193"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
+      <c r="A3" s="185"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="186"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="191"/>
+      <c r="F3" s="192"/>
+      <c r="G3" s="192"/>
       <c r="H3" s="146"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="187"/>
-      <c r="B4" s="188"/>
-      <c r="C4" s="188"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="196"/>
-      <c r="G4" s="196"/>
+      <c r="A4" s="185"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="194"/>
+      <c r="G4" s="194"/>
       <c r="H4" s="147"/>
     </row>
     <row r="5" spans="1:48">
-      <c r="A5" s="187"/>
-      <c r="B5" s="188"/>
-      <c r="C5" s="188"/>
+      <c r="A5" s="185"/>
+      <c r="B5" s="186"/>
+      <c r="C5" s="186"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="123"/>
       <c r="H5" s="123"/>
     </row>
     <row r="6" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A6" s="187"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="182" t="s">
+      <c r="A6" s="185"/>
+      <c r="B6" s="186"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="197" t="s">
+      <c r="E6" s="195" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="198"/>
-      <c r="G6" s="198"/>
+      <c r="F6" s="196"/>
+      <c r="G6" s="196"/>
       <c r="H6" s="148"/>
     </row>
     <row r="7" spans="1:48">
-      <c r="A7" s="187"/>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="199"/>
-      <c r="F7" s="200"/>
-      <c r="G7" s="200"/>
+      <c r="A7" s="185"/>
+      <c r="B7" s="186"/>
+      <c r="C7" s="186"/>
+      <c r="D7" s="181"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="198"/>
+      <c r="G7" s="198"/>
       <c r="H7" s="149"/>
     </row>
     <row r="8" spans="1:48">
-      <c r="A8" s="189"/>
-      <c r="B8" s="190"/>
-      <c r="C8" s="190"/>
-      <c r="D8" s="184"/>
-      <c r="E8" s="201"/>
-      <c r="F8" s="202"/>
-      <c r="G8" s="202"/>
+      <c r="A8" s="187"/>
+      <c r="B8" s="188"/>
+      <c r="C8" s="188"/>
+      <c r="D8" s="182"/>
+      <c r="E8" s="199"/>
+      <c r="F8" s="200"/>
+      <c r="G8" s="200"/>
       <c r="H8" s="150"/>
     </row>
     <row r="12" spans="1:48">
@@ -8081,7 +8047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.6">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -8113,15 +8079,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="201" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="205"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
+      <c r="G1" s="203"/>
       <c r="H1" s="264"/>
     </row>
     <row r="2" spans="1:8">
@@ -8137,11 +8103,11 @@
       <c r="D2" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="204" t="s">
+      <c r="E2" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="204"/>
-      <c r="G2" s="206"/>
+      <c r="F2" s="202"/>
+      <c r="G2" s="204"/>
       <c r="H2" s="264"/>
     </row>
     <row r="3" spans="1:8">
@@ -8157,9 +8123,9 @@
       <c r="D3" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="208"/>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="206"/>
       <c r="H3" s="264"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
@@ -8175,23 +8141,23 @@
       <c r="D4" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="207" t="s">
+      <c r="E4" s="205" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="207"/>
-      <c r="G4" s="208"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="206"/>
       <c r="H4" s="264"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="209" t="s">
+      <c r="A5" s="207" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="210"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="210"/>
-      <c r="E5" s="210"/>
-      <c r="F5" s="210"/>
-      <c r="G5" s="211"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="209"/>
       <c r="H5" s="264"/>
     </row>
     <row r="6" spans="1:8">
@@ -9622,14 +9588,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="212" t="s">
+      <c r="A1" s="210" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="213"/>
-      <c r="C1" s="213"/>
-      <c r="D1" s="213"/>
-      <c r="E1" s="213"/>
-      <c r="F1" s="213"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -9639,10 +9605,10 @@
       <c r="B2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="212" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="215"/>
+      <c r="D2" s="213"/>
       <c r="E2" s="40" t="s">
         <v>25</v>
       </c>
@@ -9658,10 +9624,10 @@
       <c r="B3" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="216" t="s">
+      <c r="C3" s="214" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="217"/>
+      <c r="D3" s="215"/>
       <c r="E3" s="41" t="s">
         <v>29</v>
       </c>
@@ -9677,10 +9643,10 @@
       <c r="B4" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="214" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="217"/>
+      <c r="D4" s="215"/>
       <c r="E4" s="41" t="s">
         <v>32</v>
       </c>
@@ -9689,14 +9655,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="213" t="s">
+      <c r="A5" s="211" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="213"/>
-      <c r="C5" s="213"/>
-      <c r="D5" s="213"/>
-      <c r="E5" s="213"/>
-      <c r="F5" s="213"/>
+      <c r="B5" s="211"/>
+      <c r="C5" s="211"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="211"/>
+      <c r="F5" s="211"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="40" t="s">
@@ -9826,14 +9792,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="216" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="46" t="s">
@@ -9842,10 +9808,10 @@
       <c r="B2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="220" t="s">
+      <c r="C2" s="218" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="221"/>
+      <c r="D2" s="219"/>
       <c r="E2" s="46" t="s">
         <v>25</v>
       </c>
@@ -9860,10 +9826,10 @@
       <c r="B3" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="222" t="s">
+      <c r="C3" s="220" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="223"/>
+      <c r="D3" s="221"/>
       <c r="E3" s="47" t="s">
         <v>29</v>
       </c>
@@ -9876,10 +9842,10 @@
       <c r="B4" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="224" t="s">
+      <c r="C4" s="222" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="225"/>
+      <c r="D4" s="223"/>
       <c r="E4" s="49" t="s">
         <v>191</v>
       </c>
@@ -9896,13 +9862,13 @@
       <c r="F5" s="271"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="220" t="s">
+      <c r="A7" s="218" t="s">
         <v>193</v>
       </c>
-      <c r="B7" s="226"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
+      <c r="B7" s="224"/>
+      <c r="C7" s="224"/>
+      <c r="D7" s="224"/>
+      <c r="E7" s="224"/>
       <c r="F7" s="271"/>
     </row>
     <row r="8" spans="1:6">
@@ -10074,13 +10040,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="229" t="s">
+      <c r="A1" s="227" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="230"/>
-      <c r="C1" s="230"/>
-      <c r="D1" s="230"/>
-      <c r="E1" s="231"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="229"/>
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
@@ -10181,39 +10147,39 @@
       <c r="E7" s="30"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="229" t="s">
+      <c r="A8" s="227" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="230"/>
-      <c r="C8" s="230"/>
-      <c r="D8" s="230"/>
-      <c r="E8" s="230"/>
+      <c r="B8" s="228"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="232" t="s">
+      <c r="A9" s="230" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="233" t="s">
+      <c r="B9" s="231" t="s">
         <v>222</v>
       </c>
-      <c r="C9" s="233" t="s">
+      <c r="C9" s="231" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="234" t="s">
+      <c r="D9" s="232" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="234" t="s">
+      <c r="E9" s="232" t="s">
         <v>223</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="232"/>
-      <c r="B10" s="233"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
+      <c r="A10" s="230"/>
+      <c r="B10" s="231"/>
+      <c r="C10" s="231"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6">
@@ -11243,13 +11209,13 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="227" t="s">
+      <c r="A68" s="225" t="s">
         <v>240</v>
       </c>
-      <c r="B68" s="228"/>
-      <c r="C68" s="228"/>
-      <c r="D68" s="228"/>
-      <c r="E68" s="228"/>
+      <c r="B68" s="226"/>
+      <c r="C68" s="226"/>
+      <c r="D68" s="226"/>
+      <c r="E68" s="226"/>
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
@@ -12298,13 +12264,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="236" t="s">
+      <c r="A1" s="234" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="237"/>
-      <c r="C1" s="237"/>
-      <c r="D1" s="237"/>
-      <c r="E1" s="238"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="236"/>
       <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6">
@@ -12351,13 +12317,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="239" t="s">
+      <c r="A5" s="237" t="s">
         <v>272</v>
       </c>
-      <c r="B5" s="239"/>
-      <c r="C5" s="239"/>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
+      <c r="B5" s="237"/>
+      <c r="C5" s="237"/>
+      <c r="D5" s="237"/>
+      <c r="E5" s="237"/>
       <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6">
@@ -12540,13 +12506,13 @@
       <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="179" t="s">
+      <c r="A5" s="238" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="179"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="179"/>
+      <c r="B5" s="238"/>
+      <c r="C5" s="238"/>
+      <c r="D5" s="238"/>
+      <c r="E5" s="238"/>
     </row>
     <row r="6" spans="1:5" ht="24.75">
       <c r="A6" s="21" t="s">
@@ -12892,14 +12858,14 @@
       <c r="G12" s="105"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
-      <c r="A13" s="178" t="s">
+      <c r="A13" s="239" t="s">
         <v>220</v>
       </c>
-      <c r="B13" s="178"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="178"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="179"/>
+      <c r="B13" s="239"/>
+      <c r="C13" s="239"/>
+      <c r="D13" s="239"/>
+      <c r="E13" s="239"/>
+      <c r="F13" s="238"/>
       <c r="G13" s="144"/>
     </row>
     <row r="14" spans="1:8" ht="27">
